--- a/data/merged/2026-10-08/MERGED_ES_Spot-Cleaner_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_ES_Spot-Cleaner_2026-10-08.xlsx
@@ -7014,50 +7014,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7383,7 +7339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16588,40 +16544,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Clean &amp; Restore Carpet Cleaner Formula – CCS04</t>
+          <t>HAUSHOF StainZapper Pro Aspiradora de Agua para Tapicerías, 450WsLimpiador de Manchas con Detergente y Cepillo para Sofás,</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DDPL3PD2?psc=1</t>
+          <t>https://www.amazon.es/dp/B0D2HFLM1C?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16635,13 +16591,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>7788</v>
+        <v>32262</v>
       </c>
       <c r="P41" s="15">
-        <v>1462</v>
+        <v>25124</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16650,61 +16606,55 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="U41" s="16">
-        <v>0.07</v>
+        <v>1.07</v>
       </c>
       <c r="V41" s="15">
-        <v>3478</v>
-      </c>
-      <c r="W41" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X41" s="15">
-        <v>1999</v>
-      </c>
+        <v>3440</v>
+      </c>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
       <c r="Y41" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>19.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="19">
-        <v>681</v>
+        <v>732</v>
       </c>
       <c r="AE41" s="15">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.1954</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="AH41" s="20">
-        <v>5.58</v>
+        <v>7.03</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.57</v>
+        <v>0.76</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>775</v>
+        <v>804</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
@@ -16715,7 +16665,7 @@
       <c r="AO41" s="13"/>
       <c r="AP41"/>
       <c r="AQ41" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR41" s="19">
         <v>1</v>
@@ -16747,7 +16697,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13"/>
+      <c r="BD41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
@@ -16759,47 +16713,47 @@
       </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>2,03 kg</t>
+          <t>3.85 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>3.85 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>25 x 16,8 x 7,6 cm</t>
+          <t>19.6 x 38.5 x 30 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
+          <t>19.60 x 38.50 x 30.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>25 x 16.8 x 7.6 cm</t>
+          <t>44.4 x 33.9 x 20 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
+          <t>44.40 x 33.90 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16764,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -16822,28 +16776,28 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Pro Aspiradora de Agua para Tapicerías, 450WsLimpiador de Manchas con Detergente y Cepillo para Sofás,</t>
+          <t>HAUSHOF StainZapper Aspiradora de Agua para Tapicerías, 400WsLimpiador de Manchas para Sofás, Moquetas y Tapicerías con Asp</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D2HFLM1C?psc=1</t>
+          <t>https://www.amazon.es/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16857,13 +16811,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>32262</v>
+        <v>22022</v>
       </c>
       <c r="P42" s="15">
-        <v>25124</v>
+        <v>26260</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16872,17 +16826,17 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U42" s="16">
-        <v>1.07</v>
+        <v>-0.2</v>
       </c>
       <c r="V42" s="15">
-        <v>3440</v>
+        <v>3128</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
@@ -16890,41 +16844,41 @@
         <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>89.99</v>
+        <v>67.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>732</v>
+        <v>4799</v>
       </c>
       <c r="AE42" s="15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.09300000000000001</v>
+        <v>0.3261</v>
       </c>
       <c r="AH42" s="20">
-        <v>7.03</v>
+        <v>8.37</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>804</v>
+        <v>1248</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
@@ -16934,7 +16888,7 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
@@ -16943,7 +16897,7 @@
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU42" s="13"/>
@@ -16979,47 +16933,43 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>3.85 kg</t>
+          <t>3,4 Kilogramos</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>3.85 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>19.6 x 38.5 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>19.60 x 38.50 x 30.00 cm</t>
-        </is>
-      </c>
+          <t>15f. x 28,5an. x 26,5al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.9 x 20 cm</t>
+          <t>40.2 x 34.2 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.90 x 20.00 cm</t>
+          <t>40.20 x 34.20 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17030,40 +16980,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0G444QZVN</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Greenote</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/Greenote/page/6E7904DA-FB53-4592-9F78-2F85A1DF65D6?lp_asin=B0G444QZVN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Aspiradora de Agua para Tapicerías, 400WsLimpiador de Manchas para Sofás, Moquetas y Tapicerías con Asp</t>
+          <t>Greenote Limpiador de Alfombras 600W,4 Ruedas Giratorias para Máxima Maniobrabilidad, Almacenamiento Compacto,Autolimpieza de</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.es/dp/B0G444QZVN?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71pwzi4bRWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0G444QZVN</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17077,13 +17027,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>22022</v>
+        <v>13557</v>
       </c>
       <c r="P43" s="15">
-        <v>26260</v>
+        <v>104419</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17092,17 +17042,17 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.2</v>
+        <v>0.41</v>
       </c>
       <c r="V43" s="15">
-        <v>3128</v>
+        <v>2851</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
@@ -17110,51 +17060,51 @@
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>67.99</v>
+        <v>71.07</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>4799</v>
+        <v>39</v>
       </c>
       <c r="AE43" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.3261</v>
+        <v>0.1026</v>
       </c>
       <c r="AH43" s="20">
-        <v>8.37</v>
+        <v>7.35</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>1248</v>
+        <v>203</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR43" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
@@ -17163,7 +17113,7 @@
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AU43" s="13"/>
@@ -17199,43 +17149,47 @@
       </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilogramos</t>
+          <t>3.2 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>15f. x 28,5an. x 26,5al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
+          <t>40 x 18 x 30 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23" t="inlineStr">
+        <is>
+          <t>40.00 x 18.00 x 30.00 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>4.5 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>44.7 x 33.8 x 19.8 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>44.70 x 33.80 x 19.80 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17246,40 +17200,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0G444QZVN</t>
+          <t>B0DSC939TV</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Greenote</t>
+          <t>CLEANmaxx</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Greenote/page/6E7904DA-FB53-4592-9F78-2F85A1DF65D6?lp_asin=B0G444QZVN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Greenote Limpiador de Alfombras 600W,4 Ruedas Giratorias para Máxima Maniobrabilidad, Almacenamiento Compacto,Autolimpieza de</t>
+          <t>CLEANmaxx Limpiador de tapicería Pro de 400 W, potente aspiradora de lavado con función de autolimpieza y 2 boquillas, ideal</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0G444QZVN?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DSC939TV?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71pwzi4bRWL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61SoXvnOcdL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0G444QZVN</t>
+          <t>B0DSC939TV</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17293,13 +17247,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>13557</v>
+        <v>18544</v>
       </c>
       <c r="P44" s="15">
-        <v>104419</v>
+        <v>29169</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17308,59 +17262,59 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U44" s="16">
-        <v>0.41</v>
+        <v>1.1</v>
       </c>
       <c r="V44" s="15">
-        <v>2851</v>
+        <v>2671</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
       <c r="Y44" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z44" s="20">
-        <v>71.07</v>
+        <v>94.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="19">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="AE44" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.1026</v>
+        <v>0.0789</v>
       </c>
       <c r="AH44" s="20">
-        <v>7.35</v>
+        <v>9.06</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>203</v>
+        <v>637</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -17370,92 +17324,88 @@
         <v>8</v>
       </c>
       <c r="AR44" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>DS e-Sales GmbH</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU44" s="13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AV44" s="14" t="inlineStr">
+        <is>
+          <t>Stapelfeld 22145 DE</t>
+        </is>
+      </c>
+      <c r="AW44" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K</t>
+        </is>
+      </c>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="13"/>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
+      <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>3.20 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>40 x 18 x 30 cm</t>
+          <t>33.5 x 29.5 x 33 cm</t>
         </is>
       </c>
       <c r="BM44" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 18.00 x 30.00 cm</t>
+          <t>33.50 x 29.50 x 33.00 cm</t>
         </is>
       </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.5 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>44.7 x 33.8 x 19.8 cm</t>
+          <t>36.9 x 34.5 x 28.5 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>44.70 x 33.80 x 19.80 cm</t>
+          <t>36.90 x 34.50 x 28.50 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17466,40 +17416,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0DSC939TV</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
+          <t>https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx Limpiador de tapicería Pro de 400 W, potente aspiradora de lavado con función de autolimpieza y 2 boquillas, ideal</t>
+          <t>Akitas Limpiador para Moquetas y Tapicerías 1L Baja Espuma Fragancia Floral Para Alfombras Sofás Asientos de Coche Elimina Ol</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DSC939TV?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DX2J6DW2?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61SoXvnOcdL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0DSC939TV</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17513,13 +17463,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>18544</v>
+        <v>11034</v>
       </c>
       <c r="P45" s="15">
-        <v>29169</v>
+        <v>117</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17528,150 +17478,168 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="U45" s="16">
-        <v>1.1</v>
+        <v>-0.77</v>
       </c>
       <c r="V45" s="15">
-        <v>2671</v>
-      </c>
-      <c r="W45" s="15"/>
-      <c r="X45" s="15"/>
+        <v>2234</v>
+      </c>
+      <c r="W45" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X45" s="15">
+        <v>750</v>
+      </c>
       <c r="Y45" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>94.99</v>
+        <v>14.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="AE45" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.0789</v>
+        <v>0.0604</v>
       </c>
       <c r="AH45" s="20">
-        <v>9.06</v>
+        <v>4.27</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>637</v>
+        <v>441</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
       <c r="AQ45" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>DS e-Sales GmbH</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>Stapelfeld 22145 DE</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
-      <c r="BC45" s="13"/>
+      <c r="BC45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23"/>
+      <c r="BI45" s="23" t="inlineStr">
+        <is>
+          <t>Opción Amazon</t>
+        </is>
+      </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>1.1 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>1.10 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>33.5 x 29.5 x 33 cm</t>
+          <t>15 x 27 x 28 cm</t>
         </is>
       </c>
       <c r="BM45" s="23" t="inlineStr">
         <is>
-          <t>33.50 x 29.50 x 33.00 cm</t>
+          <t>15.00 x 27.00 x 28.00 cm</t>
         </is>
       </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>36.9 x 34.5 x 28.5 cm</t>
+          <t>24 x 8.3 x 7.7 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>36.90 x 34.50 x 28.50 cm</t>
+          <t>24.00 x 8.30 x 7.70 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -17682,40 +17650,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0DX2J6DW2</t>
+          <t>B0HCBKNGZB</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0HCBKNGZB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Akitas Limpiador para Moquetas y Tapicerías 1L Baja Espuma Fragancia Floral Para Alfombras Sofás Asientos de Coche Elimina Ol</t>
+          <t>Cecotec Limpiador Aspirador Tapicerías Conga Carpet&amp;Spot Clean 7500 ProsCon Cable, 750W, Succión de hasta 17kPa, 2 Depósito</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DX2J6DW2?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HCBKNGZB?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/711mfHaqVPL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0DX2J6DW2</t>
+          <t>B0HCBKNGZB</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17729,13 +17697,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>11034</v>
+        <v>30549</v>
       </c>
       <c r="P46" s="15">
-        <v>117</v>
+        <v>149356</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.01</v>
+        <v>0.83</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17744,168 +17712,138 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>149</v>
-      </c>
-      <c r="U46" s="16">
-        <v>-0.77</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>2234</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>750</v>
-      </c>
+        <v>2198</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>14.99</v>
+        <v>98.35</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="AE46" s="15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.0604</v>
+        <v>0.0909</v>
       </c>
       <c r="AH46" s="20">
-        <v>4.27</v>
+        <v>9.06</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.57</v>
+        <v>0.76</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>441</v>
+        <v>62</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
-      <c r="AQ46" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ46" s="19"/>
       <c r="AR46" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU46" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV46" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
-      <c r="AW46" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU46" s="13"/>
+      <c r="AV46" s="14"/>
+      <c r="AW46" s="13"/>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>4.44 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>4.44 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>15 x 27 x 28 cm</t>
+          <t>24.6 x 31.5 x 33.6 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>15.00 x 27.00 x 28.00 cm</t>
+          <t>24.60 x 31.50 x 33.60 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>1.12 kg</t>
+          <t>6.31 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.12 kg</t>
+          <t>6.31 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>24 x 8.3 x 7.7 cm</t>
+          <t>37.5 x 36.2 x 26 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>24.00 x 8.30 x 7.70 cm</t>
+          <t>37.50 x 36.20 x 26.00 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17916,40 +17854,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0HCBKNGZB</t>
+          <t>B0F7RBRJXK</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Mellerware</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0HCBKNGZB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/Mellerware/page/86D7248E-73C5-488B-A9F5-DCEF95165E79?lp_asin=B0F7RBRJXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Limpiador Aspirador Tapicerías Conga Carpet&amp;Spot Clean 7500 ProsCon Cable, 750W, Succión de hasta 17kPa, 2 Depósito</t>
+          <t>Mellerware - Aspirador para Tapicería Cleany Carpet 600wsLimpieza eficaz con función Wet&amp;Dry | Boquilla 2 en 1 | Succión Du</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0HCBKNGZB?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F7RBRJXK?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/711mfHaqVPL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51yMkWfZgTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0HCBKNGZB</t>
+          <t>B0F7RBRJXK</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -17963,13 +17901,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>30549</v>
+        <v>32222</v>
       </c>
       <c r="P47" s="15">
-        <v>149356</v>
+        <v>199944</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -17978,15 +17916,17 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>22</v>
-      </c>
-      <c r="U47" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="U47" s="16">
+        <v>-0.94</v>
+      </c>
       <c r="V47" s="15">
-        <v>2198</v>
+        <v>560</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
@@ -17994,69 +17934,87 @@
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>98.35</v>
+        <v>84.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE47" s="15">
         <v>2</v>
       </c>
       <c r="AF47" s="21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.0909</v>
+        <v>0.25</v>
       </c>
       <c r="AH47" s="20">
-        <v>9.06</v>
+        <v>8.37</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>62</v>
+        <v>518</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
-      <c r="AQ47" s="19"/>
+      <c r="AQ47" s="19">
+        <v>9</v>
+      </c>
       <c r="AR47" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>SDA Europe SLU</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>BARCELONA 08130 ES</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17U01KUHAVJDO</t>
+        </is>
+      </c>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18069,42 +18027,38 @@
       <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>4.44 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>4.44 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>24.6 x 31.5 x 33.6 cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="23" t="inlineStr">
-        <is>
-          <t>24.60 x 31.50 x 33.60 cm</t>
-        </is>
-      </c>
+          <t>35,8l. x 26,5an. x 29,5al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM47" s="23"/>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>6.31 kg</t>
+          <t>3.51 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>6.31 kg</t>
+          <t>3.51 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>37.5 x 36.2 x 26 cm</t>
+          <t>35.8 x 29.5 x 26.5 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>37.50 x 36.20 x 26.00 cm</t>
+          <t>35.80 x 29.50 x 26.50 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -18120,40 +18074,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0F7RBRJXK</t>
+          <t>B0HBCB6GRG</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Mellerware</t>
+          <t>Circlio</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Mellerware/page/86D7248E-73C5-488B-A9F5-DCEF95165E79?lp_asin=B0F7RBRJXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Mellerware - Aspirador para Tapicería Cleany Carpet 600wsLimpieza eficaz con función Wet&amp;Dry | Boquilla 2 en 1 | Succión Du</t>
+          <t>Aspiradora sin Cable 58Kpa/600W/75Min para Suelos/Alfombras/Pelo de AnimalesAspiradora sin Cable de 1.6 L/Pantalla Táctil L</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F7RBRJXK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HBCB6GRG?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51yMkWfZgTL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0F7RBRJXK</t>
+          <t>B0HBCB6GRG</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18167,13 +18121,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>32222</v>
+        <v>24869</v>
       </c>
       <c r="P48" s="15">
-        <v>199944</v>
+        <v>332380</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18182,17 +18136,15 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>8</v>
-      </c>
-      <c r="U48" s="16">
-        <v>-0.94</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -18200,79 +18152,83 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>84.99</v>
+        <v>149.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE48" s="15">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>8.37</v>
+        <v>6.15</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>518</v>
+        <v>37</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>SDA Europe SLU</t>
+          <t>Zenithor es</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>BARCELONA 08130 ES</t>
+          <t>Romania 234555 RO</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17U01KUHAVJDO</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13"/>
+      <c r="AY48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
@@ -18290,46 +18246,50 @@
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23"/>
+      <c r="BI48" s="23" t="inlineStr">
+        <is>
+          <t>Opción Amazon</t>
+        </is>
+      </c>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
+          <t>4 Kilogramos</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>35,8l. x 26,5an. x 29,5al. centímetros</t>
+          <t>5l. x 5an. x 5al. centímetros</t>
         </is>
       </c>
       <c r="BM48" s="23"/>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>3.51 kg</t>
+          <t>4.18 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>3.51 kg</t>
+          <t>4.18 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>35.8 x 29.5 x 26.5 cm</t>
+          <t>43.7 x 33.8 x 18.7 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>35.80 x 29.50 x 26.50 cm</t>
+          <t>43.70 x 33.80 x 18.70 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18340,224 +18300,104 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0HBCB6GRG</t>
+          <t>B0FWBRM3VK</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Circlio</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora sin Cable 58Kpa/600W/75Min para Suelos/Alfombras/Pelo de AnimalesAspiradora sin Cable de 1.6 L/Pantalla Táctil L</t>
+          <t>K?rcher SE 2 Spot</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0HBCB6GRG?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FWBRM3VK?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61H6hgXckNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0HBCB6GRG</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>24869</v>
-      </c>
-      <c r="P49" s="15">
-        <v>332380</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>0.74</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>3</v>
-      </c>
+          <t>B0FWBRM3VK</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
       <c r="U49" s="16"/>
-      <c r="V49" s="15">
-        <v>450</v>
-      </c>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="20">
-        <v>149.99</v>
-      </c>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
-      <c r="AH49" s="20">
-        <v>6.15</v>
-      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.81</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>37</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>Zenithor es</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>Romania 234555 RO</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
-      <c r="AY49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>4 Kilogramos</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>4.00 kg</t>
-        </is>
-      </c>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>5l. x 5an. x 5al. centímetros</t>
-        </is>
-      </c>
+      <c r="BI49" s="23"/>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
+      <c r="BL49" s="23"/>
       <c r="BM49" s="23"/>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>4.18 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>4.18 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>43.7 x 33.8 x 18.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>43.70 x 33.80 x 18.70 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
     <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
@@ -18566,7 +18406,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0FWBRM3VK</t>
+          <t>B0H5L383SW</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -18579,23 +18419,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>K?rcher SE 2 Spot</t>
+          <t>Livatro Limpia Tapicerías a Vapor 100°C para Sofás y Tejidoss2100 W, vapor listo en 30 s para ayudar a desprender los resid</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FWBRM3VK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H5L383SW?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61H6hgXckNL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0FWBRM3VK</t>
+          <t>B0H5L383SW</t>
         </is>
       </c>
       <c r="M50" s="14"/>
@@ -18616,11 +18456,11 @@
       <c r="AB50"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AE50" s="15"/>
       <c r="AF50" s="21">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
@@ -18664,112 +18504,6 @@
       <c r="BP50" s="23"/>
       <c r="BQ50" s="23"/>
       <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H5L383SW</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Livatro Limpia Tapicerías a Vapor 100°C para Sofás y Tejidoss2100 W, vapor listo en 30 s para ayudar a desprender los resid</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0H5L383SW?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H5L383SW</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>6</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19060,85 +18794,78 @@
     <hyperlink ref="M40" r:id="rId283" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N40" r:id="rId284"/>
     <hyperlink ref="AW40" r:id="rId285" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
-    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
-    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.es/dp/B0DDPL3PD2?psc=1"/>
-    <hyperlink ref="K41" r:id="rId289" tooltip="https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
+    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.es/dp/B0D2HFLM1C"/>
+    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.es/dp/B0D2HFLM1C?psc=1"/>
+    <hyperlink ref="K41" r:id="rId289" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.es/dp/B0D2HFLM1C"/>
     <hyperlink ref="M41" r:id="rId291" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N41" r:id="rId292"/>
-    <hyperlink ref="C42" r:id="rId293" tooltip="https://www.amazon.es/dp/B0D2HFLM1C"/>
-    <hyperlink ref="G42" r:id="rId294" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId295" tooltip="https://www.amazon.es/dp/B0D2HFLM1C?psc=1"/>
-    <hyperlink ref="K42" r:id="rId296" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId297" tooltip="https://www.amazon.es/dp/B0D2HFLM1C"/>
+    <hyperlink ref="C42" r:id="rId293" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G42" r:id="rId294" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId295" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K42" r:id="rId296" tooltip="https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId297" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
     <hyperlink ref="M42" r:id="rId298" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N42" r:id="rId299"/>
-    <hyperlink ref="C43" r:id="rId300" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G43" r:id="rId301" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId302" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K43" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId304" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="C43" r:id="rId300" tooltip="https://www.amazon.es/dp/B0G444QZVN"/>
+    <hyperlink ref="G43" r:id="rId301" tooltip="https://www.amazon.es/stores/Greenote/page/6E7904DA-FB53-4592-9F78-2F85A1DF65D6?lp_asin=B0G444QZVN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId302" tooltip="https://www.amazon.es/dp/B0G444QZVN?psc=1"/>
+    <hyperlink ref="K43" r:id="rId303" tooltip="https://images-na.ssl-images-amazon.com/images/I/71pwzi4bRWL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId304" tooltip="https://www.amazon.es/dp/B0G444QZVN"/>
     <hyperlink ref="M43" r:id="rId305" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N43" r:id="rId306"/>
-    <hyperlink ref="C44" r:id="rId307" tooltip="https://www.amazon.es/dp/B0G444QZVN"/>
-    <hyperlink ref="G44" r:id="rId308" tooltip="https://www.amazon.es/stores/Greenote/page/6E7904DA-FB53-4592-9F78-2F85A1DF65D6?lp_asin=B0G444QZVN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId309" tooltip="https://www.amazon.es/dp/B0G444QZVN?psc=1"/>
-    <hyperlink ref="K44" r:id="rId310" tooltip="https://images-na.ssl-images-amazon.com/images/I/71pwzi4bRWL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId311" tooltip="https://www.amazon.es/dp/B0G444QZVN"/>
+    <hyperlink ref="C44" r:id="rId307" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
+    <hyperlink ref="G44" r:id="rId308" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
+    <hyperlink ref="J44" r:id="rId309" tooltip="https://www.amazon.es/dp/B0DSC939TV?psc=1"/>
+    <hyperlink ref="K44" r:id="rId310" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SoXvnOcdL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId311" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
     <hyperlink ref="M44" r:id="rId312" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N44" r:id="rId313"/>
-    <hyperlink ref="C45" r:id="rId314" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
-    <hyperlink ref="G45" r:id="rId315" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
-    <hyperlink ref="J45" r:id="rId316" tooltip="https://www.amazon.es/dp/B0DSC939TV?psc=1"/>
-    <hyperlink ref="K45" r:id="rId317" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SoXvnOcdL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId318" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
-    <hyperlink ref="M45" r:id="rId319" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N45" r:id="rId320"/>
-    <hyperlink ref="AW45" r:id="rId321" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K"/>
-    <hyperlink ref="C46" r:id="rId322" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
-    <hyperlink ref="G46" r:id="rId323" tooltip="https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId324" tooltip="https://www.amazon.es/dp/B0DX2J6DW2?psc=1"/>
-    <hyperlink ref="K46" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId326" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
-    <hyperlink ref="M46" r:id="rId327" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N46" r:id="rId328"/>
-    <hyperlink ref="AW46" r:id="rId329" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C47" r:id="rId330" tooltip="https://www.amazon.es/dp/B0HCBKNGZB"/>
-    <hyperlink ref="G47" r:id="rId331" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0HCBKNGZB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId332" tooltip="https://www.amazon.es/dp/B0HCBKNGZB?psc=1"/>
-    <hyperlink ref="K47" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/711mfHaqVPL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId334" tooltip="https://www.amazon.es/dp/B0HCBKNGZB"/>
+    <hyperlink ref="AW44" r:id="rId314" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K"/>
+    <hyperlink ref="C45" r:id="rId315" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
+    <hyperlink ref="G45" r:id="rId316" tooltip="https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId317" tooltip="https://www.amazon.es/dp/B0DX2J6DW2?psc=1"/>
+    <hyperlink ref="K45" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId319" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
+    <hyperlink ref="M45" r:id="rId320" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N45" r:id="rId321"/>
+    <hyperlink ref="AW45" r:id="rId322" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C46" r:id="rId323" tooltip="https://www.amazon.es/dp/B0HCBKNGZB"/>
+    <hyperlink ref="G46" r:id="rId324" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0HCBKNGZB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId325" tooltip="https://www.amazon.es/dp/B0HCBKNGZB?psc=1"/>
+    <hyperlink ref="K46" r:id="rId326" tooltip="https://images-na.ssl-images-amazon.com/images/I/711mfHaqVPL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId327" tooltip="https://www.amazon.es/dp/B0HCBKNGZB"/>
+    <hyperlink ref="M46" r:id="rId328" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N46" r:id="rId329"/>
+    <hyperlink ref="C47" r:id="rId330" tooltip="https://www.amazon.es/dp/B0F7RBRJXK"/>
+    <hyperlink ref="G47" r:id="rId331" tooltip="https://www.amazon.es/stores/Mellerware/page/86D7248E-73C5-488B-A9F5-DCEF95165E79?lp_asin=B0F7RBRJXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J47" r:id="rId332" tooltip="https://www.amazon.es/dp/B0F7RBRJXK?psc=1"/>
+    <hyperlink ref="K47" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/51yMkWfZgTL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId334" tooltip="https://www.amazon.es/dp/B0F7RBRJXK"/>
     <hyperlink ref="M47" r:id="rId335" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N47" r:id="rId336"/>
-    <hyperlink ref="C48" r:id="rId337" tooltip="https://www.amazon.es/dp/B0F7RBRJXK"/>
-    <hyperlink ref="G48" r:id="rId338" tooltip="https://www.amazon.es/stores/Mellerware/page/86D7248E-73C5-488B-A9F5-DCEF95165E79?lp_asin=B0F7RBRJXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId339" tooltip="https://www.amazon.es/dp/B0F7RBRJXK?psc=1"/>
-    <hyperlink ref="K48" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/51yMkWfZgTL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId341" tooltip="https://www.amazon.es/dp/B0F7RBRJXK"/>
-    <hyperlink ref="M48" r:id="rId342" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N48" r:id="rId343"/>
-    <hyperlink ref="AW48" r:id="rId344" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17U01KUHAVJDO"/>
-    <hyperlink ref="C49" r:id="rId345" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
-    <hyperlink ref="G49" r:id="rId346" tooltip="https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId347" tooltip="https://www.amazon.es/dp/B0HBCB6GRG?psc=1"/>
-    <hyperlink ref="K49" r:id="rId348" tooltip="https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId349" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
-    <hyperlink ref="M49" r:id="rId350" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N49" r:id="rId351"/>
-    <hyperlink ref="AW49" r:id="rId352" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08"/>
-    <hyperlink ref="C50" r:id="rId353" tooltip="https://www.amazon.es/dp/B0FWBRM3VK"/>
-    <hyperlink ref="G50" r:id="rId354" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J50" r:id="rId355" tooltip="https://www.amazon.es/dp/B0FWBRM3VK?psc=1"/>
-    <hyperlink ref="K50" r:id="rId356" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61H6hgXckNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId357" tooltip="https://www.amazon.es/dp/B0FWBRM3VK"/>
-    <hyperlink ref="C51" r:id="rId358" tooltip="https://www.amazon.es/dp/B0H5L383SW"/>
-    <hyperlink ref="G51" r:id="rId359" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J51" r:id="rId360" tooltip="https://www.amazon.es/dp/B0H5L383SW?psc=1"/>
-    <hyperlink ref="K51" r:id="rId361" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId362" tooltip="https://www.amazon.es/dp/B0H5L383SW"/>
+    <hyperlink ref="AW47" r:id="rId337" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17U01KUHAVJDO"/>
+    <hyperlink ref="C48" r:id="rId338" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
+    <hyperlink ref="G48" r:id="rId339" tooltip="https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId340" tooltip="https://www.amazon.es/dp/B0HBCB6GRG?psc=1"/>
+    <hyperlink ref="K48" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId342" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
+    <hyperlink ref="M48" r:id="rId343" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N48" r:id="rId344"/>
+    <hyperlink ref="AW48" r:id="rId345" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08"/>
+    <hyperlink ref="C49" r:id="rId346" tooltip="https://www.amazon.es/dp/B0FWBRM3VK"/>
+    <hyperlink ref="G49" r:id="rId347" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J49" r:id="rId348" tooltip="https://www.amazon.es/dp/B0FWBRM3VK?psc=1"/>
+    <hyperlink ref="K49" r:id="rId349" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61H6hgXckNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId350" tooltip="https://www.amazon.es/dp/B0FWBRM3VK"/>
+    <hyperlink ref="C50" r:id="rId351" tooltip="https://www.amazon.es/dp/B0H5L383SW"/>
+    <hyperlink ref="G50" r:id="rId352" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J50" r:id="rId353" tooltip="https://www.amazon.es/dp/B0H5L383SW?psc=1"/>
+    <hyperlink ref="K50" r:id="rId354" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId355" tooltip="https://www.amazon.es/dp/B0H5L383SW"/>
   </hyperlinks>
-  <drawing r:id="rId363"/>
+  <drawing r:id="rId356"/>
 </worksheet>
 </file>
 
@@ -19208,7 +18935,7 @@
         <v>116.94672855879753</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2987321711568938</v>
+        <v>0.3022044088176353</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19229,7 +18956,7 @@
         <v>88.09719175076788</v>
       </c>
       <c r="G3" s="22">
-        <v>0.30097728473322766</v>
+        <v>0.30447561790247163</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19250,7 +18977,7 @@
         <v>142.4240305149396</v>
       </c>
       <c r="G4" s="22">
-        <v>0.10386951928156365</v>
+        <v>0.10507682030728123</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19260,18 +18987,18 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <v>964</v>
+        <v>790</v>
       </c>
       <c r="C5" s="15">
-        <v>65593</v>
+        <v>62115</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>68.04253112033194</v>
+        <v>78.62658227848101</v>
       </c>
       <c r="G5" s="22">
-        <v>0.06365557316428949</v>
+        <v>0.052772211088844355</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19292,7 +19019,7 @@
         <v>167.83954154727795</v>
       </c>
       <c r="G6" s="22">
-        <v>0.023045430533544638</v>
+        <v>0.023313293253173013</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19313,7 +19040,7 @@
         <v>55.095286885245905</v>
       </c>
       <c r="G7" s="22">
-        <v>0.06444796619123085</v>
+        <v>0.06519706078824315</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19334,7 +19061,7 @@
         <v>69.99064171122994</v>
       </c>
       <c r="G8" s="22">
-        <v>0.049392498679344955</v>
+        <v>0.049966599866399466</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19355,7 +19082,7 @@
         <v>163.5</v>
       </c>
       <c r="G9" s="22">
-        <v>0.008848388800845219</v>
+        <v>0.00895123580494322</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19376,7 +19103,7 @@
         <v>89.98947368421052</v>
       </c>
       <c r="G10" s="22">
-        <v>0.012546222926571579</v>
+        <v>0.012692050768203072</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19397,7 +19124,7 @@
         <v>65.99183673469388</v>
       </c>
       <c r="G11" s="22">
-        <v>0.016178024300052826</v>
+        <v>0.016366065464261857</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19418,7 +19145,7 @@
         <v>65.13669064748201</v>
       </c>
       <c r="G12" s="22">
-        <v>0.009178552562070787</v>
+        <v>0.009285237140948564</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19439,7 +19166,7 @@
         <v>69.89922480620154</v>
       </c>
       <c r="G13" s="22">
-        <v>0.008518225039619652</v>
+        <v>0.008617234468937876</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19460,7 +19187,7 @@
         <v>119.98666666666666</v>
       </c>
       <c r="G14" s="22">
-        <v>0.004952456418383518</v>
+        <v>0.00501002004008016</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19481,7 +19208,7 @@
         <v>279.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.001716851558372953</v>
+        <v>0.0017368069472277889</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19502,7 +19229,7 @@
         <v>73.79775280898876</v>
       </c>
       <c r="G16" s="22">
-        <v>0.005876914949815108</v>
+        <v>0.005945223780895123</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19523,7 +19250,7 @@
         <v>150.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0027733755942947703</v>
+        <v>0.0028056112224448897</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19544,7 +19271,7 @@
         <v>82.67605633802818</v>
       </c>
       <c r="G18" s="22">
-        <v>0.004688325409403064</v>
+        <v>0.0047428189712758854</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19565,7 +19292,7 @@
         <v>53.19191919191919</v>
       </c>
       <c r="G19" s="22">
-        <v>0.006537242472266244</v>
+        <v>0.006613226452905812</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19586,7 +19313,7 @@
         <v>123.5</v>
       </c>
       <c r="G20" s="22">
-        <v>0.002509244585314316</v>
+        <v>0.0025384101536406146</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19607,7 +19334,7 @@
         <v>74.98333333333333</v>
       </c>
       <c r="G21" s="22">
-        <v>0.003961965134706815</v>
+        <v>0.004008016032064128</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19628,7 +19355,7 @@
         <v>130.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0019809825673534074</v>
+        <v>0.002004008016032064</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19649,7 +19376,7 @@
         <v>73.1025641025641</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0025752773375594296</v>
+        <v>0.0026052104208416833</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19670,7 +19397,7 @@
         <v>70.28947368421052</v>
       </c>
       <c r="G24" s="22">
-        <v>0.002509244585314316</v>
+        <v>0.0025384101536406146</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19691,7 +19418,7 @@
         <v>70.0</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0005282620179609086</v>
+        <v>0.0005344021376085504</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19774,18 +19501,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>12472</v>
+        <v>12298</v>
       </c>
       <c r="C2" s="15">
-        <v>1322435</v>
+        <v>1318957</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>106.0323123797306</v>
+        <v>107.24971540087819</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8235604860010565</v>
+        <v>0.8215096860387442</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19806,7 +19533,7 @@
         <v>55.095286885245905</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06444796619123085</v>
+        <v>0.06519706078824315</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19827,7 +19554,7 @@
         <v>69.99064171122994</v>
       </c>
       <c r="G4" s="22">
-        <v>0.049392498679344955</v>
+        <v>0.049966599866399466</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19848,7 +19575,7 @@
         <v>255.28947368421052</v>
       </c>
       <c r="G5" s="22">
-        <v>0.005018489170628632</v>
+        <v>0.005076820307281229</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19869,7 +19596,7 @@
         <v>65.99183673469388</v>
       </c>
       <c r="G6" s="22">
-        <v>0.016178024300052826</v>
+        <v>0.016366065464261857</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19890,7 +19617,7 @@
         <v>89.99264705882354</v>
       </c>
       <c r="G7" s="22">
-        <v>0.008980454305335447</v>
+        <v>0.009084836339345358</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19911,7 +19638,7 @@
         <v>65.13669064748201</v>
       </c>
       <c r="G8" s="22">
-        <v>0.009178552562070787</v>
+        <v>0.009285237140948564</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19932,7 +19659,7 @@
         <v>119.98666666666666</v>
       </c>
       <c r="G9" s="22">
-        <v>0.004952456418383518</v>
+        <v>0.00501002004008016</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19953,7 +19680,7 @@
         <v>150.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.0025752773375594296</v>
+        <v>0.0026052104208416833</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19974,7 +19701,7 @@
         <v>53.19191919191919</v>
       </c>
       <c r="G11" s="22">
-        <v>0.006537242472266244</v>
+        <v>0.006613226452905812</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19995,7 +19722,7 @@
         <v>74.98333333333333</v>
       </c>
       <c r="G12" s="22">
-        <v>0.003961965134706815</v>
+        <v>0.004008016032064128</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20016,7 +19743,7 @@
         <v>130.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0019809825673534074</v>
+        <v>0.002004008016032064</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20037,7 +19764,7 @@
         <v>70.28947368421052</v>
       </c>
       <c r="G14" s="22">
-        <v>0.002509244585314316</v>
+        <v>0.0025384101536406146</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20058,7 +19785,7 @@
         <v>70.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0005282620179609086</v>
+        <v>0.0005344021376085504</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20079,7 +19806,7 @@
         <v>150.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.00019809825673534074</v>
+        <v>0.0002004008016032064</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
